--- a/templates/1120_WTB_Template.xlsx
+++ b/templates/1120_WTB_Template.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -274,8 +274,19 @@
       <color rgb="FF1B3A5C"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F07840"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -372,8 +383,20 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+        <bgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E7"/>
+        <bgColor rgb="00FFF8E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -481,6 +504,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -492,7 +534,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -797,6 +839,34 @@
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4032,7 +4102,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="52.5" customHeight="1" s="52">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="111" t="inlineStr">
         <is>
           <t>SCHEDULE M-3 — Net Income (Loss) Reconciliation for Corps With Total Assets ≥ $10M</t>
         </is>
@@ -4048,7 +4118,7 @@
       <c r="D2" s="94" t="n"/>
     </row>
     <row r="3" ht="43.5" customHeight="1" s="52">
-      <c r="A3" s="95" t="inlineStr">
+      <c r="A3" s="111" t="inlineStr">
         <is>
           <t>This tab is a PLACEHOLDER. Only required if total assets ≥ $10M or voluntary election.</t>
         </is>
@@ -4175,7 +4245,7 @@
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="52">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>BALANCE SHEET (Assets)</t>
         </is>
@@ -4307,7 +4377,7 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="52">
-      <c r="A13" s="79" t="inlineStr">
+      <c r="A13" s="109" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
@@ -4427,7 +4497,7 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="52">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="109" t="inlineStr">
         <is>
           <t>Other Assets</t>
         </is>
@@ -4447,27 +4517,27 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="52">
-      <c r="A20" s="99" t="inlineStr">
+      <c r="A20" s="112" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B20" s="100">
+      <c r="B20" s="110">
         <f>SUM(B7:B19)</f>
         <v/>
       </c>
-      <c r="D20" s="100">
+      <c r="D20" s="110">
         <f>SUM(D7:D19)</f>
         <v/>
       </c>
-      <c r="F20" s="101" t="inlineStr">
+      <c r="F20" s="113" t="inlineStr">
         <is>
           <t>Sch L Ln 15</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="52">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr">
         <is>
           <t>BALANCE SHEET (Liabilities)</t>
         </is>
@@ -4519,7 +4589,7 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="52">
-      <c r="A24" s="79" t="inlineStr">
+      <c r="A24" s="109" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
@@ -4579,7 +4649,7 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="52">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="109" t="inlineStr">
         <is>
           <t>Other Liabilities</t>
         </is>
@@ -4599,22 +4669,22 @@
       </c>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="52">
-      <c r="A28" s="99" t="inlineStr">
+      <c r="A28" s="112" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B28" s="100">
+      <c r="B28" s="110">
         <f>SUM(B22:B27)</f>
         <v/>
       </c>
-      <c r="D28" s="100">
+      <c r="D28" s="110">
         <f>SUM(D22:D27)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="52">
-      <c r="A29" s="77" t="inlineStr">
+      <c r="A29" s="104" t="inlineStr">
         <is>
           <t>BALANCE SHEET (Equity)</t>
         </is>
@@ -4726,16 +4796,16 @@
       </c>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="52">
-      <c r="A35" s="99" t="inlineStr">
+      <c r="A35" s="112" t="inlineStr">
         <is>
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="B35" s="100">
+      <c r="B35" s="110">
         <f>SUM(B30:B34)</f>
         <v/>
       </c>
-      <c r="D35" s="100">
+      <c r="D35" s="110">
         <f>SUM(D30:D34)</f>
         <v/>
       </c>
@@ -4757,7 +4827,7 @@
     </row>
     <row r="37"/>
     <row r="38" ht="21.75" customHeight="1" s="52">
-      <c r="A38" s="77" t="inlineStr">
+      <c r="A38" s="104" t="inlineStr">
         <is>
           <t>INCOME (Page 1)</t>
         </is>
@@ -4769,20 +4839,20 @@
       <c r="F38" s="78" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="52">
-      <c r="A39" s="79" t="inlineStr">
+      <c r="A39" s="106" t="inlineStr">
         <is>
           <t>Gross Receipts / Sales</t>
         </is>
       </c>
-      <c r="B39" s="80">
+      <c r="B39" s="108">
         <f>'PBC - P&amp;L'!B6</f>
         <v/>
       </c>
-      <c r="D39" s="80">
+      <c r="D39" s="108">
         <f>B39+C39</f>
         <v/>
       </c>
-      <c r="F39" s="75" t="inlineStr">
+      <c r="F39" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 1a</t>
         </is>
@@ -4809,27 +4879,27 @@
       </c>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="52">
-      <c r="A41" s="79" t="inlineStr">
+      <c r="A41" s="106" t="inlineStr">
         <is>
           <t>Net Sales</t>
         </is>
       </c>
-      <c r="B41" s="80">
+      <c r="B41" s="108">
         <f>'PBC - P&amp;L'!B8</f>
         <v/>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="108">
         <f>B41+C41</f>
         <v/>
       </c>
-      <c r="F41" s="75" t="inlineStr">
+      <c r="F41" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 1c</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="52">
-      <c r="A42" s="79" t="inlineStr">
+      <c r="A42" s="109" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
@@ -4849,20 +4919,20 @@
       </c>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="52">
-      <c r="A43" s="79" t="inlineStr">
+      <c r="A43" s="106" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B43" s="80">
+      <c r="B43" s="108">
         <f>'PBC - P&amp;L'!B13</f>
         <v/>
       </c>
-      <c r="D43" s="80">
+      <c r="D43" s="108">
         <f>B43+C43</f>
         <v/>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 3</t>
         </is>
@@ -4917,44 +4987,44 @@
       </c>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="52">
-      <c r="A46" s="79" t="inlineStr">
+      <c r="A46" s="106" t="inlineStr">
         <is>
           <t>Gross Rents</t>
         </is>
       </c>
-      <c r="B46" s="80">
+      <c r="B46" s="108">
         <f>'PBC - P&amp;L'!B9</f>
         <v/>
       </c>
-      <c r="C46" s="80">
+      <c r="C46" s="108">
         <f>-'PBC - P&amp;L'!B9</f>
         <v/>
       </c>
-      <c r="D46" s="80">
+      <c r="D46" s="108">
         <f>B46+C46</f>
         <v/>
       </c>
-      <c r="F46" s="75" t="inlineStr">
+      <c r="F46" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 6</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="52">
-      <c r="A47" s="79" t="inlineStr">
+      <c r="A47" s="106" t="inlineStr">
         <is>
           <t>Gross Royalties</t>
         </is>
       </c>
-      <c r="B47" s="80">
+      <c r="B47" s="108">
         <f>'PBC - P&amp;L'!B22</f>
         <v/>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="108">
         <f>B47+C47</f>
         <v/>
       </c>
-      <c r="F47" s="75" t="inlineStr">
+      <c r="F47" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 7</t>
         </is>
@@ -4985,31 +5055,31 @@
       </c>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="52">
-      <c r="A49" s="79" t="inlineStr">
+      <c r="A49" s="106" t="inlineStr">
         <is>
           <t>Net Gain/Loss (Form 4797)</t>
         </is>
       </c>
-      <c r="B49" s="80">
+      <c r="B49" s="108">
         <f>'PBC - P&amp;L'!B19</f>
         <v/>
       </c>
-      <c r="C49" s="80">
+      <c r="C49" s="108">
         <f>-'PBC - P&amp;L'!B19</f>
         <v/>
       </c>
-      <c r="D49" s="80">
+      <c r="D49" s="108">
         <f>B49+C49</f>
         <v/>
       </c>
-      <c r="F49" s="75" t="inlineStr">
+      <c r="F49" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 9</t>
         </is>
       </c>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="52">
-      <c r="A50" s="79" t="inlineStr">
+      <c r="A50" s="109" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
@@ -5085,24 +5155,24 @@
       </c>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="52">
-      <c r="A53" s="99" t="inlineStr">
+      <c r="A53" s="112" t="inlineStr">
         <is>
           <t>TOTAL INCOME (Pg 1 Ln 11)</t>
         </is>
       </c>
-      <c r="B53" s="100">
+      <c r="B53" s="110">
         <f>B43+SUM(B44:B52)</f>
         <v/>
       </c>
-      <c r="C53" s="100">
+      <c r="C53" s="110">
         <f>SUM(C44:C52)</f>
         <v/>
       </c>
-      <c r="D53" s="100">
+      <c r="D53" s="110">
         <f>B53+C53</f>
         <v/>
       </c>
-      <c r="F53" s="101" t="inlineStr">
+      <c r="F53" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 11</t>
         </is>
@@ -5110,7 +5180,7 @@
     </row>
     <row r="54"/>
     <row r="55" ht="21.75" customHeight="1" s="52">
-      <c r="A55" s="77" t="inlineStr">
+      <c r="A55" s="104" t="inlineStr">
         <is>
           <t>DEDUCTIONS (Page 1)</t>
         </is>
@@ -5122,7 +5192,7 @@
       <c r="F55" s="78" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="52">
-      <c r="A56" s="79" t="inlineStr">
+      <c r="A56" s="109" t="inlineStr">
         <is>
           <t>Officer Compensation</t>
         </is>
@@ -5688,7 +5758,7 @@
       </c>
     </row>
     <row r="79" ht="21.75" customHeight="1" s="52">
-      <c r="A79" s="79" t="inlineStr">
+      <c r="A79" s="109" t="inlineStr">
         <is>
           <t>Rental Activity Expenses</t>
         </is>
@@ -5712,7 +5782,7 @@
       </c>
     </row>
     <row r="80" ht="21.75" customHeight="1" s="52">
-      <c r="A80" s="79" t="inlineStr">
+      <c r="A80" s="109" t="inlineStr">
         <is>
           <t>Other Deductions</t>
         </is>
@@ -5732,24 +5802,24 @@
       </c>
     </row>
     <row r="81" ht="21.75" customHeight="1" s="52">
-      <c r="A81" s="99" t="inlineStr">
+      <c r="A81" s="112" t="inlineStr">
         <is>
           <t>TOTAL DEDUCTIONS (Pg 1 Ln 27)</t>
         </is>
       </c>
-      <c r="B81" s="100">
+      <c r="B81" s="110">
         <f>SUM(B56:B80)</f>
         <v/>
       </c>
-      <c r="C81" s="100">
+      <c r="C81" s="110">
         <f>SUM(C56:C80)</f>
         <v/>
       </c>
-      <c r="D81" s="100">
+      <c r="D81" s="110">
         <f>B81+C81</f>
         <v/>
       </c>
-      <c r="F81" s="101" t="inlineStr">
+      <c r="F81" s="113" t="inlineStr">
         <is>
           <t>Pg 1 Ln 27</t>
         </is>
@@ -5844,7 +5914,7 @@
     </row>
     <row r="89"/>
     <row r="90" ht="21.75" customHeight="1" s="52">
-      <c r="A90" s="77" t="inlineStr">
+      <c r="A90" s="104" t="inlineStr">
         <is>
           <t>DISTRIBUTIONS</t>
         </is>
@@ -5895,20 +5965,20 @@
       </c>
     </row>
     <row r="94" ht="21.75" customHeight="1" s="52">
-      <c r="A94" s="99" t="inlineStr">
+      <c r="A94" s="112" t="inlineStr">
         <is>
           <t>TOTAL DISTRIBUTIONS</t>
         </is>
       </c>
-      <c r="B94" s="100">
+      <c r="B94" s="110">
         <f>SUM(B91:B93)</f>
         <v/>
       </c>
-      <c r="D94" s="100">
+      <c r="D94" s="110">
         <f>B94+C94</f>
         <v/>
       </c>
-      <c r="F94" s="101" t="inlineStr">
+      <c r="F94" s="113" t="inlineStr">
         <is>
           <t>M-2</t>
         </is>
@@ -5916,7 +5986,7 @@
     </row>
     <row r="95"/>
     <row r="96" ht="21.75" customHeight="1" s="52">
-      <c r="A96" s="77" t="inlineStr">
+      <c r="A96" s="104" t="inlineStr">
         <is>
           <t>M-1 RECONCILIATION PROOF</t>
         </is>
@@ -6035,20 +6105,20 @@
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="52">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B5" s="78" t="n"/>
+      <c r="B5" s="105" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="52">
-      <c r="A6" s="79" t="inlineStr">
+      <c r="A6" s="106" t="inlineStr">
         <is>
           <t>Gross Receipts / Sales</t>
         </is>
       </c>
-      <c r="B6" s="80" t="n"/>
+      <c r="B6" s="107" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="52">
       <c r="A7" s="79" t="inlineStr">
@@ -6056,15 +6126,15 @@
           <t>Returns &amp; Allowances</t>
         </is>
       </c>
-      <c r="B7" s="80" t="n"/>
+      <c r="B7" s="107" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="52">
-      <c r="A8" s="79" t="inlineStr">
+      <c r="A8" s="106" t="inlineStr">
         <is>
           <t>Net Sales</t>
         </is>
       </c>
-      <c r="B8" s="80">
+      <c r="B8" s="108">
         <f>B6+B7</f>
         <v/>
       </c>
@@ -6075,44 +6145,50 @@
           <t>Equipment Rental Income</t>
         </is>
       </c>
-      <c r="B9" s="80" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="107" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="105" t="n"/>
+      <c r="B10" s="105" t="n"/>
+    </row>
     <row r="11" ht="21.75" customHeight="1" s="52">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>COST OF GOODS SOLD</t>
         </is>
       </c>
-      <c r="B11" s="78" t="n"/>
+      <c r="B11" s="105" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="52">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B12" s="80" t="n"/>
+      <c r="B12" s="107" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="52">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="106" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B13" s="80">
+      <c r="B13" s="108">
         <f>B8-B12</f>
         <v/>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="105" t="n"/>
+      <c r="B14" s="105" t="n"/>
+    </row>
     <row r="15" ht="21.75" customHeight="1" s="52">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>OTHER INCOME</t>
         </is>
       </c>
-      <c r="B15" s="78" t="n"/>
+      <c r="B15" s="105" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="52">
       <c r="A16" s="79" t="inlineStr">
@@ -6120,15 +6196,15 @@
           <t>Interest Income (Bank)</t>
         </is>
       </c>
-      <c r="B16" s="80" t="n"/>
+      <c r="B16" s="107" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="52">
-      <c r="A17" s="79" t="inlineStr">
+      <c r="A17" s="106" t="inlineStr">
         <is>
           <t>Dividend Income (Ordinary)</t>
         </is>
       </c>
-      <c r="B17" s="80" t="n"/>
+      <c r="B17" s="107" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="A18" s="79" t="inlineStr">
@@ -6136,7 +6212,7 @@
           <t>Capital Gain — Stock Sales (LTCG)</t>
         </is>
       </c>
-      <c r="B18" s="80" t="n"/>
+      <c r="B18" s="107" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="52">
       <c r="A19" s="79" t="inlineStr">
@@ -6144,7 +6220,7 @@
           <t>Gain on Sale of Equipment</t>
         </is>
       </c>
-      <c r="B19" s="80" t="n"/>
+      <c r="B19" s="107" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="52">
       <c r="A20" s="79" t="inlineStr">
@@ -6152,7 +6228,7 @@
           <t>Tax-Exempt Muni Bond Interest</t>
         </is>
       </c>
-      <c r="B20" s="80" t="n"/>
+      <c r="B20" s="107" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="52">
       <c r="A21" s="79" t="inlineStr">
@@ -6160,7 +6236,7 @@
           <t>Unrealized Gain on Investments</t>
         </is>
       </c>
-      <c r="B21" s="80" t="n"/>
+      <c r="B21" s="107" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="52">
       <c r="A22" s="79" t="inlineStr">
@@ -6168,52 +6244,58 @@
           <t>Royalties</t>
         </is>
       </c>
-      <c r="B22" s="80" t="n"/>
+      <c r="B22" s="107" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="52">
-      <c r="A23" s="79" t="inlineStr">
+      <c r="A23" s="109" t="inlineStr">
         <is>
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B23" s="80" t="n"/>
+      <c r="B23" s="107" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="52">
-      <c r="A24" s="81" t="inlineStr">
+      <c r="A24" s="106" t="inlineStr">
         <is>
           <t>Total Other Income</t>
         </is>
       </c>
-      <c r="B24" s="82">
+      <c r="B24" s="110">
         <f>SUM(B16:B23)</f>
         <v/>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="105" t="n"/>
+      <c r="B25" s="105" t="n"/>
+    </row>
     <row r="26" ht="21.75" customHeight="1" s="52">
-      <c r="A26" s="77" t="inlineStr">
+      <c r="A26" s="104" t="inlineStr">
         <is>
           <t>OFFICER COMPENSATION</t>
         </is>
       </c>
-      <c r="B26" s="78" t="n"/>
+      <c r="B26" s="105" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="52">
-      <c r="A27" s="79" t="inlineStr">
+      <c r="A27" s="109" t="inlineStr">
         <is>
           <t>Officer Compensation (per W-2)</t>
         </is>
       </c>
-      <c r="B27" s="80" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="B27" s="107" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="105" t="n"/>
+      <c r="B28" s="105" t="n"/>
+    </row>
     <row r="29" ht="21.75" customHeight="1" s="52">
       <c r="A29" s="77" t="inlineStr">
         <is>
           <t>SALARIES &amp; WAGES</t>
         </is>
       </c>
-      <c r="B29" s="78" t="n"/>
+      <c r="B29" s="105" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="52">
       <c r="A30" s="79" t="inlineStr">
@@ -6221,16 +6303,19 @@
           <t>Salaries &amp; Wages (non-officer)</t>
         </is>
       </c>
-      <c r="B30" s="80" t="n"/>
-    </row>
-    <row r="31"/>
+      <c r="B30" s="107" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="105" t="n"/>
+      <c r="B31" s="105" t="n"/>
+    </row>
     <row r="32" ht="21.75" customHeight="1" s="52">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="104" t="inlineStr">
         <is>
           <t>DEDUCTIONS</t>
         </is>
       </c>
-      <c r="B32" s="78" t="n"/>
+      <c r="B32" s="105" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="52">
       <c r="A33" s="79" t="inlineStr">
@@ -6238,7 +6323,7 @@
           <t>Repairs &amp; Maintenance</t>
         </is>
       </c>
-      <c r="B33" s="80" t="n"/>
+      <c r="B33" s="107" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="52">
       <c r="A34" s="79" t="inlineStr">
@@ -6246,7 +6331,7 @@
           <t>Bad Debts</t>
         </is>
       </c>
-      <c r="B34" s="80" t="n"/>
+      <c r="B34" s="107" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="52">
       <c r="A35" s="79" t="inlineStr">
@@ -6254,7 +6339,7 @@
           <t>Rents</t>
         </is>
       </c>
-      <c r="B35" s="80" t="n"/>
+      <c r="B35" s="107" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="52">
       <c r="A36" s="79" t="inlineStr">
@@ -6262,7 +6347,7 @@
           <t>Taxes &amp; Licenses</t>
         </is>
       </c>
-      <c r="B36" s="80" t="n"/>
+      <c r="B36" s="107" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="52">
       <c r="A37" s="79" t="inlineStr">
@@ -6270,7 +6355,7 @@
           <t>Interest Expense — Business Loans</t>
         </is>
       </c>
-      <c r="B37" s="80" t="n"/>
+      <c r="B37" s="107" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="52">
       <c r="A38" s="79" t="inlineStr">
@@ -6278,7 +6363,7 @@
           <t>Depreciation — Vehicles (Book)</t>
         </is>
       </c>
-      <c r="B38" s="80" t="n"/>
+      <c r="B38" s="107" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="52">
       <c r="A39" s="79" t="inlineStr">
@@ -6286,7 +6371,7 @@
           <t>Depreciation — FF&amp;E (Book)</t>
         </is>
       </c>
-      <c r="B39" s="80" t="n"/>
+      <c r="B39" s="107" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="52">
       <c r="A40" s="79" t="inlineStr">
@@ -6294,7 +6379,7 @@
           <t>Depreciation — Computers (Book)</t>
         </is>
       </c>
-      <c r="B40" s="80" t="n"/>
+      <c r="B40" s="107" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="52">
       <c r="A41" s="79" t="inlineStr">
@@ -6302,7 +6387,7 @@
           <t>Depreciation — Leasehold (Book)</t>
         </is>
       </c>
-      <c r="B41" s="80" t="n"/>
+      <c r="B41" s="107" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="52">
       <c r="A42" s="79" t="inlineStr">
@@ -6310,7 +6395,7 @@
           <t>Advertising</t>
         </is>
       </c>
-      <c r="B42" s="80" t="n"/>
+      <c r="B42" s="107" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="52">
       <c r="A43" s="79" t="inlineStr">
@@ -6318,7 +6403,7 @@
           <t>Pension/Profit-Sharing Plans</t>
         </is>
       </c>
-      <c r="B43" s="80" t="n"/>
+      <c r="B43" s="107" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="52">
       <c r="A44" s="79" t="inlineStr">
@@ -6326,7 +6411,7 @@
           <t>Employee Benefit Programs</t>
         </is>
       </c>
-      <c r="B44" s="80" t="n"/>
+      <c r="B44" s="107" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="52">
       <c r="A45" s="79" t="inlineStr">
@@ -6334,7 +6419,7 @@
           <t>Meals (Business)</t>
         </is>
       </c>
-      <c r="B45" s="80" t="n"/>
+      <c r="B45" s="107" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="52">
       <c r="A46" s="79" t="inlineStr">
@@ -6342,7 +6427,7 @@
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="B46" s="80" t="n"/>
+      <c r="B46" s="107" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="52">
       <c r="A47" s="79" t="inlineStr">
@@ -6350,7 +6435,7 @@
           <t>Charitable Contributions</t>
         </is>
       </c>
-      <c r="B47" s="80" t="n"/>
+      <c r="B47" s="107" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="52">
       <c r="A48" s="79" t="inlineStr">
@@ -6358,7 +6443,7 @@
           <t>Political Contributions</t>
         </is>
       </c>
-      <c r="B48" s="80" t="n"/>
+      <c r="B48" s="107" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="52">
       <c r="A49" s="79" t="inlineStr">
@@ -6366,7 +6451,7 @@
           <t>Penalties &amp; Fines</t>
         </is>
       </c>
-      <c r="B49" s="80" t="n"/>
+      <c r="B49" s="107" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="52">
       <c r="A50" s="79" t="inlineStr">
@@ -6374,7 +6459,7 @@
           <t>Life Insurance (Corp Beneficiary)</t>
         </is>
       </c>
-      <c r="B50" s="80" t="n"/>
+      <c r="B50" s="107" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="52">
       <c r="A51" s="79" t="inlineStr">
@@ -6382,43 +6467,46 @@
           <t>Club Dues</t>
         </is>
       </c>
-      <c r="B51" s="80" t="n"/>
+      <c r="B51" s="107" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="52">
-      <c r="A52" s="79" t="inlineStr">
+      <c r="A52" s="109" t="inlineStr">
         <is>
           <t>Rental Activity Expenses</t>
         </is>
       </c>
-      <c r="B52" s="80" t="n"/>
+      <c r="B52" s="107" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="52">
-      <c r="A53" s="79" t="inlineStr">
+      <c r="A53" s="109" t="inlineStr">
         <is>
           <t>Other Deductions</t>
         </is>
       </c>
-      <c r="B53" s="80" t="n"/>
+      <c r="B53" s="107" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="52">
-      <c r="A54" s="81" t="inlineStr">
+      <c r="A54" s="106" t="inlineStr">
         <is>
           <t>Total Deductions</t>
         </is>
       </c>
-      <c r="B54" s="82">
+      <c r="B54" s="110">
         <f>SUM(B33:B53)</f>
         <v/>
       </c>
     </row>
-    <row r="55"/>
+    <row r="55">
+      <c r="A55" s="105" t="n"/>
+      <c r="B55" s="105" t="n"/>
+    </row>
     <row r="56" ht="15" customHeight="1" s="52">
-      <c r="A56" s="81" t="inlineStr">
+      <c r="A56" s="106" t="inlineStr">
         <is>
           <t>NET INCOME (BOOK)</t>
         </is>
       </c>
-      <c r="B56" s="82">
+      <c r="B56" s="110">
         <f>B13+B9+B24-B27-B30-B54</f>
         <v/>
       </c>
@@ -6483,12 +6571,12 @@
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="52">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
       </c>
-      <c r="B5" s="78" t="n"/>
+      <c r="B5" s="105" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="52">
       <c r="A6" s="79" t="inlineStr">
@@ -6496,7 +6584,7 @@
           <t>Cash &amp; Cash Equivalents</t>
         </is>
       </c>
-      <c r="B6" s="80" t="n"/>
+      <c r="B6" s="107" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="52">
       <c r="A7" s="79" t="inlineStr">
@@ -6504,7 +6592,7 @@
           <t>Accounts Receivable (Gross)</t>
         </is>
       </c>
-      <c r="B7" s="80" t="n"/>
+      <c r="B7" s="107" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="52">
       <c r="A8" s="79" t="inlineStr">
@@ -6512,7 +6600,7 @@
           <t>Less: Allowance for Doubtful Accounts</t>
         </is>
       </c>
-      <c r="B8" s="80" t="n"/>
+      <c r="B8" s="107" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="52">
       <c r="A9" s="79" t="inlineStr">
@@ -6520,7 +6608,7 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B9" s="80" t="n"/>
+      <c r="B9" s="107" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="52">
       <c r="A10" s="79" t="inlineStr">
@@ -6528,7 +6616,7 @@
           <t>Prepaid Expenses</t>
         </is>
       </c>
-      <c r="B10" s="80" t="n"/>
+      <c r="B10" s="107" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="52">
       <c r="A11" s="79" t="inlineStr">
@@ -6536,15 +6624,15 @@
           <t>Investments — Govt Obligations</t>
         </is>
       </c>
-      <c r="B11" s="80" t="n"/>
+      <c r="B11" s="107" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="52">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="B12" s="80" t="n"/>
+      <c r="B12" s="107" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="52">
       <c r="A13" s="79" t="inlineStr">
@@ -6552,7 +6640,7 @@
           <t>Land</t>
         </is>
       </c>
-      <c r="B13" s="80" t="n"/>
+      <c r="B13" s="107" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="52">
       <c r="A14" s="79" t="inlineStr">
@@ -6560,7 +6648,7 @@
           <t>Buildings/Other Depreciable Assets</t>
         </is>
       </c>
-      <c r="B14" s="80" t="n"/>
+      <c r="B14" s="107" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="52">
       <c r="A15" s="79" t="inlineStr">
@@ -6568,7 +6656,7 @@
           <t>Depreciable Assets (Cost/Basis)</t>
         </is>
       </c>
-      <c r="B15" s="80" t="n"/>
+      <c r="B15" s="107" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="52">
       <c r="A16" s="79" t="inlineStr">
@@ -6576,7 +6664,7 @@
           <t>Less: Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B16" s="80" t="n"/>
+      <c r="B16" s="107" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="52">
       <c r="A17" s="79" t="inlineStr">
@@ -6584,7 +6672,7 @@
           <t>Intangible Assets (Amortizable)</t>
         </is>
       </c>
-      <c r="B17" s="80" t="n"/>
+      <c r="B17" s="107" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="A18" s="79" t="inlineStr">
@@ -6592,35 +6680,38 @@
           <t>Less: Accumulated Amortization</t>
         </is>
       </c>
-      <c r="B18" s="80" t="n"/>
+      <c r="B18" s="107" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="52">
-      <c r="A19" s="79" t="inlineStr">
+      <c r="A19" s="109" t="inlineStr">
         <is>
           <t>Other Assets</t>
         </is>
       </c>
-      <c r="B19" s="80" t="n"/>
+      <c r="B19" s="107" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="52">
-      <c r="A20" s="81" t="inlineStr">
+      <c r="A20" s="106" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B20" s="82">
+      <c r="B20" s="110">
         <f>SUM(B6:B19)</f>
         <v/>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" s="105" t="n"/>
+      <c r="B21" s="105" t="n"/>
+    </row>
     <row r="22" ht="21.75" customHeight="1" s="52">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="104" t="inlineStr">
         <is>
           <t>LIABILITIES</t>
         </is>
       </c>
-      <c r="B22" s="78" t="n"/>
+      <c r="B22" s="105" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="52">
       <c r="A23" s="79" t="inlineStr">
@@ -6628,7 +6719,7 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="B23" s="80" t="n"/>
+      <c r="B23" s="107" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="52">
       <c r="A24" s="79" t="inlineStr">
@@ -6636,15 +6727,15 @@
           <t>Mortgages/Notes Payable (&lt;1 yr)</t>
         </is>
       </c>
-      <c r="B24" s="80" t="n"/>
+      <c r="B24" s="107" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="52">
-      <c r="A25" s="79" t="inlineStr">
+      <c r="A25" s="109" t="inlineStr">
         <is>
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B25" s="80" t="n"/>
+      <c r="B25" s="107" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="52">
       <c r="A26" s="79" t="inlineStr">
@@ -6652,7 +6743,7 @@
           <t>Loans from Shareholders</t>
         </is>
       </c>
-      <c r="B26" s="80" t="n"/>
+      <c r="B26" s="107" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="52">
       <c r="A27" s="79" t="inlineStr">
@@ -6660,35 +6751,38 @@
           <t>Mortgages/Notes Payable (≥1 yr)</t>
         </is>
       </c>
-      <c r="B27" s="80" t="n"/>
+      <c r="B27" s="107" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="52">
-      <c r="A28" s="79" t="inlineStr">
+      <c r="A28" s="109" t="inlineStr">
         <is>
           <t>Other Liabilities</t>
         </is>
       </c>
-      <c r="B28" s="80" t="n"/>
+      <c r="B28" s="107" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="52">
-      <c r="A29" s="81" t="inlineStr">
+      <c r="A29" s="106" t="inlineStr">
         <is>
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B29" s="82">
+      <c r="B29" s="110">
         <f>SUM(B23:B28)</f>
         <v/>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="105" t="n"/>
+      <c r="B30" s="105" t="n"/>
+    </row>
     <row r="31" ht="21.75" customHeight="1" s="52">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="A31" s="104" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="B31" s="78" t="n"/>
+      <c r="B31" s="105" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="A32" s="79" t="inlineStr">
@@ -6696,7 +6790,7 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="B32" s="80" t="n"/>
+      <c r="B32" s="107" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="52">
       <c r="A33" s="79" t="inlineStr">
@@ -6704,7 +6798,7 @@
           <t>Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B33" s="80" t="n"/>
+      <c r="B33" s="107" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="52">
       <c r="A34" s="79" t="inlineStr">
@@ -6712,7 +6806,7 @@
           <t>Retained Earnings (Prior Years)</t>
         </is>
       </c>
-      <c r="B34" s="80" t="n"/>
+      <c r="B34" s="107" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="52">
       <c r="A35" s="79" t="inlineStr">
@@ -6731,33 +6825,36 @@
           <t>Less: Treasury Stock</t>
         </is>
       </c>
-      <c r="B36" s="80" t="n"/>
+      <c r="B36" s="107" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="52">
-      <c r="A37" s="81" t="inlineStr">
+      <c r="A37" s="106" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B37" s="82">
+      <c r="B37" s="110">
         <f>SUM(B32:B35)-B36</f>
         <v/>
       </c>
     </row>
-    <row r="38"/>
+    <row r="38">
+      <c r="A38" s="105" t="n"/>
+      <c r="B38" s="105" t="n"/>
+    </row>
     <row r="39" ht="15" customHeight="1" s="52">
-      <c r="A39" s="81" t="inlineStr">
+      <c r="A39" s="106" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES + EQUITY</t>
         </is>
       </c>
-      <c r="B39" s="82">
+      <c r="B39" s="110">
         <f>B29+B37</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="52">
-      <c r="A40" s="81" t="inlineStr">
+      <c r="A40" s="109" t="inlineStr">
         <is>
           <t>Balance Sheet Check (should be 0)</t>
         </is>
@@ -8324,7 +8421,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="52">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>SCHEDULE M-1 — Reconciliation of Income (Loss) per Books With Income per Return</t>
         </is>
@@ -8802,7 +8899,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="52">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>SCHEDULE L — Balance Sheets per Books</t>
         </is>
@@ -8852,7 +8949,7 @@
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="52">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="104" t="inlineStr">
         <is>
           <t>ASSETS</t>
         </is>
@@ -9216,7 +9313,7 @@
       </c>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="52">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="104" t="inlineStr">
         <is>
           <t>LIABILITIES AND SHAREHOLDERS' EQUITY</t>
         </is>
@@ -9526,7 +9623,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="35.25" customHeight="1" s="52">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>SCHEDULE M-2 — Analysis of Unappropriated Retained Earnings per Books (Ln 25, Sch L)</t>
         </is>
@@ -9705,7 +9802,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="27.75" customHeight="1" s="52">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="109" t="inlineStr">
         <is>
           <t>M-2 NOTES:</t>
         </is>
@@ -9746,7 +9843,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="52">
-      <c r="A1" s="92" t="inlineStr">
+      <c r="A1" s="109" t="inlineStr">
         <is>
           <t>SCHEDULE J — TAX COMPUTATION AND PAYMENT</t>
         </is>
